--- a/StrangerTracking.xlsx
+++ b/StrangerTracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dflet\Documents\Visual Studio Projects\SMBReader\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300A6105-0AED-4A35-BC22-149DD3D5760D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFC1712-072D-4BCC-8E26-881BFA865025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1875" windowWidth="29040" windowHeight="15720" xr2:uid="{52081DA9-6276-40E9-8738-68DD44D8405E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{52081DA9-6276-40E9-8738-68DD44D8405E}"/>
   </bookViews>
   <sheets>
     <sheet name="Function in App" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Function</t>
   </si>
@@ -50,18 +50,12 @@
     <t>Base of Ghidra</t>
   </si>
   <si>
-    <t>Offset within Stranger App</t>
-  </si>
-  <si>
     <t>LoadStrangerFiles</t>
   </si>
   <si>
     <t>This will load the 7 models that are stored in an array, which includes Stranger.smb</t>
   </si>
   <si>
-    <t xml:space="preserve">0x00212d00 </t>
-  </si>
-  <si>
     <t>LoadGEO</t>
   </si>
   <si>
@@ -71,13 +65,94 @@
     <t>Load a geometry type chunk from SMB archive</t>
   </si>
   <si>
-    <t>ReadBytesFromSMB</t>
-  </si>
-  <si>
     <t>Read n bytes from SMB file</t>
   </si>
   <si>
-    <t>0x00201a00</t>
+    <t>LoadBytesFromSMB</t>
+  </si>
+  <si>
+    <t>LoadSMBChunkHeader</t>
+  </si>
+  <si>
+    <t>LoadSMBFile</t>
+  </si>
+  <si>
+    <t>LoadSMBGeoClasses</t>
+  </si>
+  <si>
+    <t>LoadStringFromSMB</t>
+  </si>
+  <si>
+    <t>LoadTexture</t>
+  </si>
+  <si>
+    <t>Load the data for an smb chunk head</t>
+  </si>
+  <si>
+    <t>Load and process the entire SMB file</t>
+  </si>
+  <si>
+    <t>Create the type of geometry class and probably load data for geometry</t>
+  </si>
+  <si>
+    <t>All strings have a size before them, this utility loads it</t>
+  </si>
+  <si>
+    <t>Function for loading texture</t>
+  </si>
+  <si>
+    <t>0x00400000</t>
+  </si>
+  <si>
+    <t>0x00213a00</t>
+  </si>
+  <si>
+    <t>0x00212d00</t>
+  </si>
+  <si>
+    <t>0x00058ce0</t>
+  </si>
+  <si>
+    <t>0x00237b60</t>
+  </si>
+  <si>
+    <t>0x002f9ca0</t>
+  </si>
+  <si>
+    <t>0x00214df0</t>
+  </si>
+  <si>
+    <t>Offset within Stranger App from image base</t>
+  </si>
+  <si>
+    <t>0x00001b80</t>
+  </si>
+  <si>
+    <t>GeomertyDefConstructor</t>
+  </si>
+  <si>
+    <t>GeometryDestructible</t>
+  </si>
+  <si>
+    <t>GeometryHierarchyInit</t>
+  </si>
+  <si>
+    <t>0x00237740</t>
+  </si>
+  <si>
+    <t>0x0028d130</t>
+  </si>
+  <si>
+    <t>0x0022fd40</t>
+  </si>
+  <si>
+    <t>Constructor  for geometry type (multiple meshes)</t>
+  </si>
+  <si>
+    <t>Constructor  for geometry type (single mesh)</t>
+  </si>
+  <si>
+    <t>Constructor  for geometry type (destructible mesh)</t>
   </si>
 </sst>
 </file>
@@ -113,10 +188,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D3EC83D-9CD7-44D2-AAA4-7B99427EFD6F}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -450,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -461,35 +539,126 @@
     </row>
     <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
